--- a/test_data/Orion_Stress_Demo/PN-BETA-02/40202/BU02/HRM/post DDV_HRM-2031-0440/Panel 02/Front/2031-03-01_08-00-00_ENG_Orion_Stress_Demo_BU02_Front_Summary.xlsx
+++ b/test_data/Orion_Stress_Demo/PN-BETA-02/40202/BU02/HRM/post DDV_HRM-2031-0440/Panel 02/Front/2031-03-01_08-00-00_ENG_Orion_Stress_Demo_BU02_Front_Summary.xlsx
@@ -413,28 +413,38 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J40"/>
+  <dimension ref="A1:J80"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="C1" t="inlineStr">
         <is>
-          <t>Distance 1</t>
+          <t>Max Stepheight</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>Distance 2</t>
+          <t>Min Stepheight</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>Angle</t>
+          <t>Mean Stepheight</t>
         </is>
       </c>
       <c r="F1" t="inlineStr">
         <is>
-          <t>Area</t>
+          <t>Radius</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>Dimple</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>Bump</t>
         </is>
       </c>
     </row>
@@ -446,20 +456,26 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Fiducial 1</t>
+          <t>Pad 1</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>120.31641</v>
+        <v>16.80825</v>
       </c>
       <c r="D2" t="n">
-        <v>84.25867</v>
+        <v>16.79801</v>
       </c>
       <c r="E2" t="n">
-        <v>90.61982</v>
+        <v>16.80049</v>
       </c>
       <c r="F2" t="n">
-        <v>521.59707</v>
+        <v>42.19761</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0.05136</v>
+      </c>
+      <c r="H2" t="n">
+        <v>1.76854</v>
       </c>
     </row>
     <row r="3">
@@ -469,16 +485,22 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>123.84953</v>
+        <v>16.39924</v>
       </c>
       <c r="D3" t="n">
-        <v>85.34976</v>
+        <v>16.2584</v>
       </c>
       <c r="E3" t="n">
-        <v>92.51555</v>
+        <v>16.38671</v>
       </c>
       <c r="F3" t="n">
-        <v>522.0976000000001</v>
+        <v>42.02712</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0.05138</v>
+      </c>
+      <c r="H3" t="n">
+        <v>1.80237</v>
       </c>
     </row>
     <row r="4">
@@ -488,16 +510,22 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>121.92688</v>
+        <v>16.9207</v>
       </c>
       <c r="D4" t="n">
-        <v>85.02083</v>
+        <v>16.55312</v>
       </c>
       <c r="E4" t="n">
-        <v>91.09713000000001</v>
+        <v>16.66722</v>
       </c>
       <c r="F4" t="n">
-        <v>509.46393</v>
+        <v>42.22447</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0.05025</v>
+      </c>
+      <c r="H4" t="n">
+        <v>1.82177</v>
       </c>
     </row>
     <row r="5">
@@ -507,16 +535,22 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>121.40303</v>
+        <v>17.24842</v>
       </c>
       <c r="D5" t="n">
-        <v>85.54734999999999</v>
+        <v>16.37956</v>
       </c>
       <c r="E5" t="n">
-        <v>92.3926</v>
+        <v>17.03899</v>
       </c>
       <c r="F5" t="n">
-        <v>518.79887</v>
+        <v>41.69384</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0.05134</v>
+      </c>
+      <c r="H5" t="n">
+        <v>1.83139</v>
       </c>
     </row>
     <row r="6">
@@ -526,16 +560,22 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>123.04938</v>
+        <v>16.62266</v>
       </c>
       <c r="D6" t="n">
-        <v>86.49424999999999</v>
+        <v>16.50842</v>
       </c>
       <c r="E6" t="n">
-        <v>91.38489</v>
+        <v>16.50966</v>
       </c>
       <c r="F6" t="n">
-        <v>515.1662</v>
+        <v>42.01533</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0.05077</v>
+      </c>
+      <c r="H6" t="n">
+        <v>1.81533</v>
       </c>
     </row>
     <row r="7">
@@ -545,16 +585,22 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>120.43865</v>
+        <v>16.63425</v>
       </c>
       <c r="D7" t="n">
-        <v>86.06363</v>
+        <v>16.13082</v>
       </c>
       <c r="E7" t="n">
-        <v>90.71930999999999</v>
+        <v>16.57293</v>
       </c>
       <c r="F7" t="n">
-        <v>514.01962</v>
+        <v>41.33967</v>
+      </c>
+      <c r="G7" t="n">
+        <v>0.05083</v>
+      </c>
+      <c r="H7" t="n">
+        <v>1.86687</v>
       </c>
     </row>
     <row r="8">
@@ -564,16 +610,22 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>119.22778</v>
+        <v>17.03831</v>
       </c>
       <c r="D8" t="n">
-        <v>86.45479</v>
+        <v>16.55195</v>
       </c>
       <c r="E8" t="n">
-        <v>91.07467</v>
+        <v>16.97196</v>
       </c>
       <c r="F8" t="n">
-        <v>514.51845</v>
+        <v>42.77451</v>
+      </c>
+      <c r="G8" t="n">
+        <v>0.0505</v>
+      </c>
+      <c r="H8" t="n">
+        <v>1.81506</v>
       </c>
     </row>
     <row r="9">
@@ -583,16 +635,22 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>122.81864</v>
+        <v>16.90208</v>
       </c>
       <c r="D9" t="n">
-        <v>85.44877</v>
+        <v>16.2895</v>
       </c>
       <c r="E9" t="n">
-        <v>89.85621</v>
+        <v>16.87153</v>
       </c>
       <c r="F9" t="n">
-        <v>513.07191</v>
+        <v>42.23464</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0.04984</v>
+      </c>
+      <c r="H9" t="n">
+        <v>1.86792</v>
       </c>
     </row>
     <row r="10">
@@ -602,27 +660,53 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>121.42151</v>
+        <v>16.89095</v>
       </c>
       <c r="D10" t="n">
-        <v>85.92637000000001</v>
+        <v>16.23713</v>
       </c>
       <c r="E10" t="n">
-        <v>91.39888999999999</v>
+        <v>16.5383</v>
       </c>
       <c r="F10" t="n">
-        <v>512.07616</v>
+        <v>42.43757</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0.05084</v>
+      </c>
+      <c r="H10" t="n">
+        <v>1.81561</v>
       </c>
     </row>
     <row r="11">
       <c r="C11" t="inlineStr">
         <is>
-          <t>Height</t>
+          <t>Max Stepheight</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Diameter</t>
+          <t>Min Stepheight</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Mean Stepheight</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Radius</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Dimple</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Bump</t>
         </is>
       </c>
     </row>
@@ -634,14 +718,26 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Micro Bump 3</t>
+          <t>Pad 2</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>8.62796</v>
+        <v>16.82859</v>
       </c>
       <c r="D12" t="n">
-        <v>24.334</v>
+        <v>16.24135</v>
+      </c>
+      <c r="E12" t="n">
+        <v>16.62711</v>
+      </c>
+      <c r="F12" t="n">
+        <v>41.75035</v>
+      </c>
+      <c r="G12" t="n">
+        <v>0.05015</v>
+      </c>
+      <c r="H12" t="n">
+        <v>1.82069</v>
       </c>
     </row>
     <row r="13">
@@ -651,10 +747,22 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>8.59713</v>
+        <v>16.9175</v>
       </c>
       <c r="D13" t="n">
-        <v>24.20121</v>
+        <v>16.43424</v>
+      </c>
+      <c r="E13" t="n">
+        <v>16.85142</v>
+      </c>
+      <c r="F13" t="n">
+        <v>42.51761</v>
+      </c>
+      <c r="G13" t="n">
+        <v>0.05049</v>
+      </c>
+      <c r="H13" t="n">
+        <v>1.80413</v>
       </c>
     </row>
     <row r="14">
@@ -664,10 +772,22 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>8.51141</v>
+        <v>16.67151</v>
       </c>
       <c r="D14" t="n">
-        <v>24.26916</v>
+        <v>16.50234</v>
+      </c>
+      <c r="E14" t="n">
+        <v>16.60805</v>
+      </c>
+      <c r="F14" t="n">
+        <v>42.49648</v>
+      </c>
+      <c r="G14" t="n">
+        <v>0.05026</v>
+      </c>
+      <c r="H14" t="n">
+        <v>1.83719</v>
       </c>
     </row>
     <row r="15">
@@ -677,10 +797,22 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>8.64658</v>
+        <v>16.82062</v>
       </c>
       <c r="D15" t="n">
-        <v>24.32503</v>
+        <v>16.29967</v>
+      </c>
+      <c r="E15" t="n">
+        <v>16.42879</v>
+      </c>
+      <c r="F15" t="n">
+        <v>42.9084</v>
+      </c>
+      <c r="G15" t="n">
+        <v>0.0517</v>
+      </c>
+      <c r="H15" t="n">
+        <v>1.80835</v>
       </c>
     </row>
     <row r="16">
@@ -690,10 +822,22 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>8.471450000000001</v>
+        <v>16.82294</v>
       </c>
       <c r="D16" t="n">
-        <v>24.47759</v>
+        <v>16.48651</v>
+      </c>
+      <c r="E16" t="n">
+        <v>16.803</v>
+      </c>
+      <c r="F16" t="n">
+        <v>42.98576</v>
+      </c>
+      <c r="G16" t="n">
+        <v>0.05033</v>
+      </c>
+      <c r="H16" t="n">
+        <v>1.81456</v>
       </c>
     </row>
     <row r="17">
@@ -703,10 +847,22 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>8.326230000000001</v>
+        <v>16.81795</v>
       </c>
       <c r="D17" t="n">
-        <v>23.46325</v>
+        <v>16.35632</v>
+      </c>
+      <c r="E17" t="n">
+        <v>16.71344</v>
+      </c>
+      <c r="F17" t="n">
+        <v>41.70806</v>
+      </c>
+      <c r="G17" t="n">
+        <v>0.05011</v>
+      </c>
+      <c r="H17" t="n">
+        <v>1.82725</v>
       </c>
     </row>
     <row r="18">
@@ -716,10 +872,22 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>8.5863</v>
+        <v>16.77432</v>
       </c>
       <c r="D18" t="n">
-        <v>24.45767</v>
+        <v>16.60637</v>
+      </c>
+      <c r="E18" t="n">
+        <v>16.71717</v>
+      </c>
+      <c r="F18" t="n">
+        <v>42.93469</v>
+      </c>
+      <c r="G18" t="n">
+        <v>0.05014</v>
+      </c>
+      <c r="H18" t="n">
+        <v>1.80624</v>
       </c>
     </row>
     <row r="19">
@@ -729,10 +897,22 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>8.806850000000001</v>
+        <v>16.8252</v>
       </c>
       <c r="D19" t="n">
-        <v>24.27611</v>
+        <v>16.43065</v>
+      </c>
+      <c r="E19" t="n">
+        <v>16.53222</v>
+      </c>
+      <c r="F19" t="n">
+        <v>42.60288</v>
+      </c>
+      <c r="G19" t="n">
+        <v>0.05248</v>
+      </c>
+      <c r="H19" t="n">
+        <v>1.78064</v>
       </c>
     </row>
     <row r="20">
@@ -742,10 +922,22 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>8.55627</v>
+        <v>16.94373</v>
       </c>
       <c r="D20" t="n">
-        <v>24.31179</v>
+        <v>16.59355</v>
+      </c>
+      <c r="E20" t="n">
+        <v>16.70711</v>
+      </c>
+      <c r="F20" t="n">
+        <v>42.04615</v>
+      </c>
+      <c r="G20" t="n">
+        <v>0.05154</v>
+      </c>
+      <c r="H20" t="n">
+        <v>1.78494</v>
       </c>
     </row>
     <row r="21">
@@ -769,16 +961,6 @@
           <t>Radius</t>
         </is>
       </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>Dimple</t>
-        </is>
-      </c>
-      <c r="H21" t="inlineStr">
-        <is>
-          <t>Bump</t>
-        </is>
-      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -788,26 +970,20 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Pad 1</t>
+          <t>SR Pad 1</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>16.7739</v>
+        <v>15.74238</v>
       </c>
       <c r="D22" t="n">
-        <v>16.89531</v>
+        <v>15.474</v>
       </c>
       <c r="E22" t="n">
-        <v>16.53125</v>
+        <v>15.65215</v>
       </c>
       <c r="F22" t="n">
-        <v>43.62899</v>
-      </c>
-      <c r="G22" t="n">
-        <v>0.05181</v>
-      </c>
-      <c r="H22" t="n">
-        <v>1.82485</v>
+        <v>256.37441</v>
       </c>
     </row>
     <row r="23">
@@ -817,22 +993,16 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>16.97129</v>
+        <v>16.07074</v>
       </c>
       <c r="D23" t="n">
-        <v>16.54398</v>
+        <v>15.27208</v>
       </c>
       <c r="E23" t="n">
-        <v>16.60235</v>
+        <v>15.75421</v>
       </c>
       <c r="F23" t="n">
-        <v>43.15177</v>
-      </c>
-      <c r="G23" t="n">
-        <v>0.05077</v>
-      </c>
-      <c r="H23" t="n">
-        <v>1.85338</v>
+        <v>254.53057</v>
       </c>
     </row>
     <row r="24">
@@ -842,22 +1012,16 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>16.84136</v>
+        <v>15.93613</v>
       </c>
       <c r="D24" t="n">
-        <v>17.05127</v>
+        <v>15.37409</v>
       </c>
       <c r="E24" t="n">
-        <v>16.73604</v>
+        <v>15.3974</v>
       </c>
       <c r="F24" t="n">
-        <v>42.17895</v>
-      </c>
-      <c r="G24" t="n">
-        <v>0.05089</v>
-      </c>
-      <c r="H24" t="n">
-        <v>1.83879</v>
+        <v>258.62683</v>
       </c>
     </row>
     <row r="25">
@@ -867,22 +1031,16 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>16.85601</v>
+        <v>15.58815</v>
       </c>
       <c r="D25" t="n">
-        <v>16.6581</v>
+        <v>15.264</v>
       </c>
       <c r="E25" t="n">
-        <v>16.86716</v>
+        <v>15.425</v>
       </c>
       <c r="F25" t="n">
-        <v>43.73128</v>
-      </c>
-      <c r="G25" t="n">
-        <v>0.05019</v>
-      </c>
-      <c r="H25" t="n">
-        <v>1.8079</v>
+        <v>252.14508</v>
       </c>
     </row>
     <row r="26">
@@ -892,22 +1050,16 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>16.96142</v>
+        <v>16.01665</v>
       </c>
       <c r="D26" t="n">
-        <v>16.69922</v>
+        <v>15.4288</v>
       </c>
       <c r="E26" t="n">
-        <v>16.84672</v>
+        <v>15.63583</v>
       </c>
       <c r="F26" t="n">
-        <v>43.10343</v>
-      </c>
-      <c r="G26" t="n">
-        <v>0.05144</v>
-      </c>
-      <c r="H26" t="n">
-        <v>1.82723</v>
+        <v>253.23528</v>
       </c>
     </row>
     <row r="27">
@@ -917,22 +1069,16 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>17.00911</v>
+        <v>16.00013</v>
       </c>
       <c r="D27" t="n">
-        <v>16.85458</v>
+        <v>15.50684</v>
       </c>
       <c r="E27" t="n">
-        <v>16.6746</v>
+        <v>15.54295</v>
       </c>
       <c r="F27" t="n">
-        <v>43.04429</v>
-      </c>
-      <c r="G27" t="n">
-        <v>0.05095</v>
-      </c>
-      <c r="H27" t="n">
-        <v>1.82338</v>
+        <v>258.64326</v>
       </c>
     </row>
     <row r="28">
@@ -942,22 +1088,16 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>16.72698</v>
+        <v>15.79985</v>
       </c>
       <c r="D28" t="n">
-        <v>16.61873</v>
+        <v>15.56891</v>
       </c>
       <c r="E28" t="n">
-        <v>16.76586</v>
+        <v>15.66537</v>
       </c>
       <c r="F28" t="n">
-        <v>41.45674</v>
-      </c>
-      <c r="G28" t="n">
-        <v>0.0515</v>
-      </c>
-      <c r="H28" t="n">
-        <v>1.82004</v>
+        <v>251.838</v>
       </c>
     </row>
     <row r="29">
@@ -967,22 +1107,16 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>16.64992</v>
+        <v>15.94564</v>
       </c>
       <c r="D29" t="n">
-        <v>16.65199</v>
+        <v>15.55342</v>
       </c>
       <c r="E29" t="n">
-        <v>16.20721</v>
+        <v>15.70289</v>
       </c>
       <c r="F29" t="n">
-        <v>42.78176</v>
-      </c>
-      <c r="G29" t="n">
-        <v>0.05069</v>
-      </c>
-      <c r="H29" t="n">
-        <v>1.77935</v>
+        <v>253.09234</v>
       </c>
     </row>
     <row r="30">
@@ -992,63 +1126,42 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>16.91182</v>
+        <v>15.75394</v>
       </c>
       <c r="D30" t="n">
-        <v>16.34676</v>
+        <v>15.34215</v>
       </c>
       <c r="E30" t="n">
-        <v>16.70264</v>
+        <v>15.5114</v>
       </c>
       <c r="F30" t="n">
-        <v>42.89142</v>
-      </c>
-      <c r="G30" t="n">
-        <v>0.05041</v>
-      </c>
-      <c r="H30" t="n">
-        <v>1.79078</v>
+        <v>255.44059</v>
       </c>
     </row>
     <row r="31">
       <c r="C31" t="inlineStr">
         <is>
-          <t>Rz max</t>
+          <t>Max Stepheight</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Rz mean</t>
+          <t>Min Stepheight</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Rz min</t>
+          <t>Mean Stepheight</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Rz max</t>
+          <t>Width</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Ra mean</t>
-        </is>
-      </c>
-      <c r="H31" t="inlineStr">
-        <is>
-          <t>Ra Std dev</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>Ra min</t>
-        </is>
-      </c>
-      <c r="J31" t="inlineStr">
-        <is>
-          <t>Ra max</t>
+          <t>Space</t>
         </is>
       </c>
     </row>
@@ -1060,32 +1173,23 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>roughness</t>
+          <t>Trace 1</t>
         </is>
       </c>
       <c r="C32" t="n">
-        <v>0.73041</v>
+        <v>16.8718</v>
       </c>
       <c r="D32" t="n">
-        <v>0.08192000000000001</v>
+        <v>15.87249</v>
       </c>
       <c r="E32" t="n">
-        <v>0.60189</v>
+        <v>16.60976</v>
       </c>
       <c r="F32" t="n">
-        <v>0.96311</v>
+        <v>21.99768</v>
       </c>
       <c r="G32" t="n">
-        <v>0.10748</v>
-      </c>
-      <c r="H32" t="n">
-        <v>0.00775</v>
-      </c>
-      <c r="I32" t="n">
-        <v>0.09356</v>
-      </c>
-      <c r="J32" t="n">
-        <v>0.12729</v>
+        <v>34.41055</v>
       </c>
     </row>
     <row r="33">
@@ -1095,28 +1199,19 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>0.75114</v>
+        <v>16.81354</v>
       </c>
       <c r="D33" t="n">
-        <v>0.0801</v>
+        <v>16.02726</v>
       </c>
       <c r="E33" t="n">
-        <v>0.59851</v>
+        <v>16.22467</v>
       </c>
       <c r="F33" t="n">
-        <v>0.95697</v>
+        <v>21.86611</v>
       </c>
       <c r="G33" t="n">
-        <v>0.10995</v>
-      </c>
-      <c r="H33" t="n">
-        <v>0.00776</v>
-      </c>
-      <c r="I33" t="n">
-        <v>0.09421</v>
-      </c>
-      <c r="J33" t="n">
-        <v>0.12458</v>
+        <v>34.67503</v>
       </c>
     </row>
     <row r="34">
@@ -1126,28 +1221,19 @@
         </is>
       </c>
       <c r="C34" t="n">
-        <v>0.74914</v>
+        <v>16.59181</v>
       </c>
       <c r="D34" t="n">
-        <v>0.08033</v>
+        <v>16.21731</v>
       </c>
       <c r="E34" t="n">
-        <v>0.6078</v>
+        <v>16.50227</v>
       </c>
       <c r="F34" t="n">
-        <v>0.97954</v>
+        <v>21.79101</v>
       </c>
       <c r="G34" t="n">
-        <v>0.10774</v>
-      </c>
-      <c r="H34" t="n">
-        <v>0.00769</v>
-      </c>
-      <c r="I34" t="n">
-        <v>0.09304999999999999</v>
-      </c>
-      <c r="J34" t="n">
-        <v>0.12445</v>
+        <v>33.80857</v>
       </c>
     </row>
     <row r="35">
@@ -1157,28 +1243,19 @@
         </is>
       </c>
       <c r="C35" t="n">
-        <v>0.76717</v>
+        <v>16.70786</v>
       </c>
       <c r="D35" t="n">
-        <v>0.08309</v>
+        <v>15.97548</v>
       </c>
       <c r="E35" t="n">
-        <v>0.61009</v>
+        <v>16.28065</v>
       </c>
       <c r="F35" t="n">
-        <v>0.97383</v>
+        <v>21.87628</v>
       </c>
       <c r="G35" t="n">
-        <v>0.1061</v>
-      </c>
-      <c r="H35" t="n">
-        <v>0.00753</v>
-      </c>
-      <c r="I35" t="n">
-        <v>0.09174</v>
-      </c>
-      <c r="J35" t="n">
-        <v>0.12714</v>
+        <v>34.70423</v>
       </c>
     </row>
     <row r="36">
@@ -1188,28 +1265,19 @@
         </is>
       </c>
       <c r="C36" t="n">
-        <v>0.75093</v>
+        <v>16.59624</v>
       </c>
       <c r="D36" t="n">
-        <v>0.07973</v>
+        <v>16.02127</v>
       </c>
       <c r="E36" t="n">
-        <v>0.61263</v>
+        <v>16.46907</v>
       </c>
       <c r="F36" t="n">
-        <v>0.96374</v>
+        <v>21.7582</v>
       </c>
       <c r="G36" t="n">
-        <v>0.10944</v>
-      </c>
-      <c r="H36" t="n">
-        <v>0.00757</v>
-      </c>
-      <c r="I36" t="n">
-        <v>0.09328</v>
-      </c>
-      <c r="J36" t="n">
-        <v>0.12483</v>
+        <v>34.65492</v>
       </c>
     </row>
     <row r="37">
@@ -1219,28 +1287,19 @@
         </is>
       </c>
       <c r="C37" t="n">
-        <v>0.74916</v>
+        <v>16.9512</v>
       </c>
       <c r="D37" t="n">
-        <v>0.07881000000000001</v>
+        <v>16.18697</v>
       </c>
       <c r="E37" t="n">
-        <v>0.60829</v>
+        <v>16.66657</v>
       </c>
       <c r="F37" t="n">
-        <v>0.94642</v>
+        <v>21.28665</v>
       </c>
       <c r="G37" t="n">
-        <v>0.10852</v>
-      </c>
-      <c r="H37" t="n">
-        <v>0.00755</v>
-      </c>
-      <c r="I37" t="n">
-        <v>0.09095</v>
-      </c>
-      <c r="J37" t="n">
-        <v>0.12523</v>
+        <v>34.16039</v>
       </c>
     </row>
     <row r="38">
@@ -1250,28 +1309,19 @@
         </is>
       </c>
       <c r="C38" t="n">
-        <v>0.73809</v>
+        <v>16.79015</v>
       </c>
       <c r="D38" t="n">
-        <v>0.08236</v>
+        <v>16.15245</v>
       </c>
       <c r="E38" t="n">
-        <v>0.62464</v>
+        <v>16.56257</v>
       </c>
       <c r="F38" t="n">
-        <v>0.96623</v>
+        <v>22.49925</v>
       </c>
       <c r="G38" t="n">
-        <v>0.10943</v>
-      </c>
-      <c r="H38" t="n">
-        <v>0.00767</v>
-      </c>
-      <c r="I38" t="n">
-        <v>0.09332</v>
-      </c>
-      <c r="J38" t="n">
-        <v>0.12648</v>
+        <v>33.75838</v>
       </c>
     </row>
     <row r="39">
@@ -1281,28 +1331,19 @@
         </is>
       </c>
       <c r="C39" t="n">
-        <v>0.74124</v>
+        <v>16.67537</v>
       </c>
       <c r="D39" t="n">
-        <v>0.08053</v>
+        <v>16.25265</v>
       </c>
       <c r="E39" t="n">
-        <v>0.60687</v>
+        <v>16.64197</v>
       </c>
       <c r="F39" t="n">
-        <v>0.9585</v>
+        <v>21.53232</v>
       </c>
       <c r="G39" t="n">
-        <v>0.10843</v>
-      </c>
-      <c r="H39" t="n">
-        <v>0.00757</v>
-      </c>
-      <c r="I39" t="n">
-        <v>0.09451</v>
-      </c>
-      <c r="J39" t="n">
-        <v>0.12508</v>
+        <v>33.76587</v>
       </c>
     </row>
     <row r="40">
@@ -1312,28 +1353,843 @@
         </is>
       </c>
       <c r="C40" t="n">
-        <v>0.75753</v>
+        <v>16.53983</v>
       </c>
       <c r="D40" t="n">
-        <v>0.08039</v>
+        <v>15.76576</v>
       </c>
       <c r="E40" t="n">
-        <v>0.60512</v>
+        <v>16.38966</v>
       </c>
       <c r="F40" t="n">
-        <v>0.95996</v>
+        <v>22.16723</v>
       </c>
       <c r="G40" t="n">
-        <v>0.10874</v>
-      </c>
-      <c r="H40" t="n">
-        <v>0.00761</v>
-      </c>
-      <c r="I40" t="n">
-        <v>0.0935</v>
-      </c>
-      <c r="J40" t="n">
-        <v>0.12657</v>
+        <v>34.56759</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Max Stepheight</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>Min Stepheight</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>Mean Stepheight</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Width</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Space</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Unit 7</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>Trace 2</t>
+        </is>
+      </c>
+      <c r="C42" t="n">
+        <v>16.80207</v>
+      </c>
+      <c r="D42" t="n">
+        <v>15.79561</v>
+      </c>
+      <c r="E42" t="n">
+        <v>16.54004</v>
+      </c>
+      <c r="F42" t="n">
+        <v>21.56271</v>
+      </c>
+      <c r="G42" t="n">
+        <v>34.21431</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Unit 8</t>
+        </is>
+      </c>
+      <c r="C43" t="n">
+        <v>16.8716</v>
+      </c>
+      <c r="D43" t="n">
+        <v>15.96293</v>
+      </c>
+      <c r="E43" t="n">
+        <v>16.26649</v>
+      </c>
+      <c r="F43" t="n">
+        <v>21.8952</v>
+      </c>
+      <c r="G43" t="n">
+        <v>34.26</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Unit 9</t>
+        </is>
+      </c>
+      <c r="C44" t="n">
+        <v>16.68963</v>
+      </c>
+      <c r="D44" t="n">
+        <v>16.08542</v>
+      </c>
+      <c r="E44" t="n">
+        <v>16.55168</v>
+      </c>
+      <c r="F44" t="n">
+        <v>21.97386</v>
+      </c>
+      <c r="G44" t="n">
+        <v>34.30296</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Unit 4</t>
+        </is>
+      </c>
+      <c r="C45" t="n">
+        <v>16.62572</v>
+      </c>
+      <c r="D45" t="n">
+        <v>15.83743</v>
+      </c>
+      <c r="E45" t="n">
+        <v>16.33174</v>
+      </c>
+      <c r="F45" t="n">
+        <v>21.42143</v>
+      </c>
+      <c r="G45" t="n">
+        <v>34.00921</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Unit 5</t>
+        </is>
+      </c>
+      <c r="C46" t="n">
+        <v>16.72862</v>
+      </c>
+      <c r="D46" t="n">
+        <v>16.45629</v>
+      </c>
+      <c r="E46" t="n">
+        <v>16.66397</v>
+      </c>
+      <c r="F46" t="n">
+        <v>21.7659</v>
+      </c>
+      <c r="G46" t="n">
+        <v>33.81032</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Unit 6</t>
+        </is>
+      </c>
+      <c r="C47" t="n">
+        <v>16.90897</v>
+      </c>
+      <c r="D47" t="n">
+        <v>15.51496</v>
+      </c>
+      <c r="E47" t="n">
+        <v>16.3258</v>
+      </c>
+      <c r="F47" t="n">
+        <v>22.00794</v>
+      </c>
+      <c r="G47" t="n">
+        <v>34.06664</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Unit 1</t>
+        </is>
+      </c>
+      <c r="C48" t="n">
+        <v>16.6483</v>
+      </c>
+      <c r="D48" t="n">
+        <v>15.96482</v>
+      </c>
+      <c r="E48" t="n">
+        <v>16.29445</v>
+      </c>
+      <c r="F48" t="n">
+        <v>21.55386</v>
+      </c>
+      <c r="G48" t="n">
+        <v>33.45391</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Unit 2</t>
+        </is>
+      </c>
+      <c r="C49" t="n">
+        <v>16.9169</v>
+      </c>
+      <c r="D49" t="n">
+        <v>16.23689</v>
+      </c>
+      <c r="E49" t="n">
+        <v>16.41888</v>
+      </c>
+      <c r="F49" t="n">
+        <v>21.6829</v>
+      </c>
+      <c r="G49" t="n">
+        <v>34.48463</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Unit 3</t>
+        </is>
+      </c>
+      <c r="C50" t="n">
+        <v>16.77742</v>
+      </c>
+      <c r="D50" t="n">
+        <v>16.10088</v>
+      </c>
+      <c r="E50" t="n">
+        <v>16.36932</v>
+      </c>
+      <c r="F50" t="n">
+        <v>21.41458</v>
+      </c>
+      <c r="G50" t="n">
+        <v>34.3471</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>Dimple</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>Bump</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>Unit 7</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>via 1</t>
+        </is>
+      </c>
+      <c r="C52" t="n">
+        <v>0.6049</v>
+      </c>
+      <c r="D52" t="n">
+        <v>1.12159</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>Unit 8</t>
+        </is>
+      </c>
+      <c r="C53" t="n">
+        <v>0.5948600000000001</v>
+      </c>
+      <c r="D53" t="n">
+        <v>1.09603</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>Unit 9</t>
+        </is>
+      </c>
+      <c r="C54" t="n">
+        <v>0.61964</v>
+      </c>
+      <c r="D54" t="n">
+        <v>1.13615</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>Unit 4</t>
+        </is>
+      </c>
+      <c r="C55" t="n">
+        <v>0.60188</v>
+      </c>
+      <c r="D55" t="n">
+        <v>1.10685</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>Unit 5</t>
+        </is>
+      </c>
+      <c r="C56" t="n">
+        <v>0.59688</v>
+      </c>
+      <c r="D56" t="n">
+        <v>1.10215</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>Unit 6</t>
+        </is>
+      </c>
+      <c r="C57" t="n">
+        <v>0.60096</v>
+      </c>
+      <c r="D57" t="n">
+        <v>1.11805</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>Unit 1</t>
+        </is>
+      </c>
+      <c r="C58" t="n">
+        <v>0.60139</v>
+      </c>
+      <c r="D58" t="n">
+        <v>1.11489</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>Unit 2</t>
+        </is>
+      </c>
+      <c r="C59" t="n">
+        <v>0.60346</v>
+      </c>
+      <c r="D59" t="n">
+        <v>1.10104</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>Unit 3</t>
+        </is>
+      </c>
+      <c r="C60" t="n">
+        <v>0.6254</v>
+      </c>
+      <c r="D60" t="n">
+        <v>1.13</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>Dimple</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>Bump</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>Unit 7</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>via 2</t>
+        </is>
+      </c>
+      <c r="C62" t="n">
+        <v>0.61497</v>
+      </c>
+      <c r="D62" t="n">
+        <v>1.1088</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>Unit 8</t>
+        </is>
+      </c>
+      <c r="C63" t="n">
+        <v>0.60499</v>
+      </c>
+      <c r="D63" t="n">
+        <v>1.09164</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>Unit 9</t>
+        </is>
+      </c>
+      <c r="C64" t="n">
+        <v>0.59688</v>
+      </c>
+      <c r="D64" t="n">
+        <v>1.11885</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>Unit 4</t>
+        </is>
+      </c>
+      <c r="C65" t="n">
+        <v>0.59621</v>
+      </c>
+      <c r="D65" t="n">
+        <v>1.11813</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>Unit 5</t>
+        </is>
+      </c>
+      <c r="C66" t="n">
+        <v>0.60401</v>
+      </c>
+      <c r="D66" t="n">
+        <v>1.08852</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>Unit 6</t>
+        </is>
+      </c>
+      <c r="C67" t="n">
+        <v>0.6048</v>
+      </c>
+      <c r="D67" t="n">
+        <v>1.13723</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>Unit 1</t>
+        </is>
+      </c>
+      <c r="C68" t="n">
+        <v>0.61246</v>
+      </c>
+      <c r="D68" t="n">
+        <v>1.14247</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>Unit 2</t>
+        </is>
+      </c>
+      <c r="C69" t="n">
+        <v>0.60022</v>
+      </c>
+      <c r="D69" t="n">
+        <v>1.12073</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>Unit 3</t>
+        </is>
+      </c>
+      <c r="C70" t="n">
+        <v>0.6079</v>
+      </c>
+      <c r="D70" t="n">
+        <v>1.10036</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>Rz max</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>Rz mean</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>Rz min</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>Rz max</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>Ra mean</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>Ra Std dev</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>Ra min</t>
+        </is>
+      </c>
+      <c r="J71" t="inlineStr">
+        <is>
+          <t>Ra max</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>Unit 7</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>roughness</t>
+        </is>
+      </c>
+      <c r="C72" t="n">
+        <v>0.74939</v>
+      </c>
+      <c r="D72" t="n">
+        <v>0.08173999999999999</v>
+      </c>
+      <c r="E72" t="n">
+        <v>0.60206</v>
+      </c>
+      <c r="F72" t="n">
+        <v>0.94437</v>
+      </c>
+      <c r="G72" t="n">
+        <v>0.10916</v>
+      </c>
+      <c r="H72" t="n">
+        <v>0.00752</v>
+      </c>
+      <c r="I72" t="n">
+        <v>0.09289</v>
+      </c>
+      <c r="J72" t="n">
+        <v>0.12589</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>Unit 8</t>
+        </is>
+      </c>
+      <c r="C73" t="n">
+        <v>0.76117</v>
+      </c>
+      <c r="D73" t="n">
+        <v>0.08179</v>
+      </c>
+      <c r="E73" t="n">
+        <v>0.6131</v>
+      </c>
+      <c r="F73" t="n">
+        <v>0.96239</v>
+      </c>
+      <c r="G73" t="n">
+        <v>0.11067</v>
+      </c>
+      <c r="H73" t="n">
+        <v>0.00743</v>
+      </c>
+      <c r="I73" t="n">
+        <v>0.09370000000000001</v>
+      </c>
+      <c r="J73" t="n">
+        <v>0.12677</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>Unit 9</t>
+        </is>
+      </c>
+      <c r="C74" t="n">
+        <v>0.73772</v>
+      </c>
+      <c r="D74" t="n">
+        <v>0.08204</v>
+      </c>
+      <c r="E74" t="n">
+        <v>0.59954</v>
+      </c>
+      <c r="F74" t="n">
+        <v>0.95936</v>
+      </c>
+      <c r="G74" t="n">
+        <v>0.10908</v>
+      </c>
+      <c r="H74" t="n">
+        <v>0.00758</v>
+      </c>
+      <c r="I74" t="n">
+        <v>0.0931</v>
+      </c>
+      <c r="J74" t="n">
+        <v>0.12362</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>Unit 4</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>0.75623</v>
+      </c>
+      <c r="D75" t="n">
+        <v>0.0815</v>
+      </c>
+      <c r="E75" t="n">
+        <v>0.60067</v>
+      </c>
+      <c r="F75" t="n">
+        <v>0.94457</v>
+      </c>
+      <c r="G75" t="n">
+        <v>0.10923</v>
+      </c>
+      <c r="H75" t="n">
+        <v>0.00758</v>
+      </c>
+      <c r="I75" t="n">
+        <v>0.09365</v>
+      </c>
+      <c r="J75" t="n">
+        <v>0.12511</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>Unit 5</t>
+        </is>
+      </c>
+      <c r="C76" t="n">
+        <v>0.74749</v>
+      </c>
+      <c r="D76" t="n">
+        <v>0.08179</v>
+      </c>
+      <c r="E76" t="n">
+        <v>0.6030799999999999</v>
+      </c>
+      <c r="F76" t="n">
+        <v>0.96933</v>
+      </c>
+      <c r="G76" t="n">
+        <v>0.11005</v>
+      </c>
+      <c r="H76" t="n">
+        <v>0.00757</v>
+      </c>
+      <c r="I76" t="n">
+        <v>0.09148000000000001</v>
+      </c>
+      <c r="J76" t="n">
+        <v>0.12628</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>Unit 6</t>
+        </is>
+      </c>
+      <c r="C77" t="n">
+        <v>0.74152</v>
+      </c>
+      <c r="D77" t="n">
+        <v>0.08126</v>
+      </c>
+      <c r="E77" t="n">
+        <v>0.60982</v>
+      </c>
+      <c r="F77" t="n">
+        <v>0.9704700000000001</v>
+      </c>
+      <c r="G77" t="n">
+        <v>0.10683</v>
+      </c>
+      <c r="H77" t="n">
+        <v>0.00764</v>
+      </c>
+      <c r="I77" t="n">
+        <v>0.09235</v>
+      </c>
+      <c r="J77" t="n">
+        <v>0.12931</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>Unit 1</t>
+        </is>
+      </c>
+      <c r="C78" t="n">
+        <v>0.75683</v>
+      </c>
+      <c r="D78" t="n">
+        <v>0.08031000000000001</v>
+      </c>
+      <c r="E78" t="n">
+        <v>0.60315</v>
+      </c>
+      <c r="F78" t="n">
+        <v>0.95961</v>
+      </c>
+      <c r="G78" t="n">
+        <v>0.10812</v>
+      </c>
+      <c r="H78" t="n">
+        <v>0.00766</v>
+      </c>
+      <c r="I78" t="n">
+        <v>0.09395000000000001</v>
+      </c>
+      <c r="J78" t="n">
+        <v>0.12653</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>Unit 2</t>
+        </is>
+      </c>
+      <c r="C79" t="n">
+        <v>0.75026</v>
+      </c>
+      <c r="D79" t="n">
+        <v>0.08180999999999999</v>
+      </c>
+      <c r="E79" t="n">
+        <v>0.60128</v>
+      </c>
+      <c r="F79" t="n">
+        <v>0.9645</v>
+      </c>
+      <c r="G79" t="n">
+        <v>0.10833</v>
+      </c>
+      <c r="H79" t="n">
+        <v>0.00781</v>
+      </c>
+      <c r="I79" t="n">
+        <v>0.09349</v>
+      </c>
+      <c r="J79" t="n">
+        <v>0.13069</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>Unit 3</t>
+        </is>
+      </c>
+      <c r="C80" t="n">
+        <v>0.7425</v>
+      </c>
+      <c r="D80" t="n">
+        <v>0.08179</v>
+      </c>
+      <c r="E80" t="n">
+        <v>0.61585</v>
+      </c>
+      <c r="F80" t="n">
+        <v>0.9462</v>
+      </c>
+      <c r="G80" t="n">
+        <v>0.10824</v>
+      </c>
+      <c r="H80" t="n">
+        <v>0.00752</v>
+      </c>
+      <c r="I80" t="n">
+        <v>0.09379</v>
+      </c>
+      <c r="J80" t="n">
+        <v>0.12738</v>
       </c>
     </row>
   </sheetData>
